--- a/AAII_Financials/Quarterly/FCNC.A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FCNC.A_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>FCNC.A</t>
   </si>
@@ -656,85 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2253000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2329000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2365000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2382000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2288000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2401000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2413000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>502000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1152000</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -762,37 +768,43 @@
       <c r="K9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2253000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2329000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2365000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2382000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2288000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2401000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2413000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>502000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1152000</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -804,8 +816,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -833,8 +846,11 @@
       <c r="K12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -862,37 +878,43 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>46000</v>
+        <v>75000</v>
       </c>
       <c r="E14" s="3">
+        <v>49000</v>
+      </c>
+      <c r="F14" s="3">
         <v>44000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>60000</v>
       </c>
-      <c r="G14" s="3">
-        <v>199000</v>
-      </c>
       <c r="H14" s="3">
+        <v>202000</v>
+      </c>
+      <c r="I14" s="3">
         <v>109000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>150000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-9796000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -900,28 +922,31 @@
         <v>42000</v>
       </c>
       <c r="E15" s="3">
+        <v>42000</v>
+      </c>
+      <c r="F15" s="3">
         <v>6000</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
       <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>118300</v>
+      </c>
+      <c r="I15" s="3">
         <v>133300</v>
       </c>
-      <c r="H15" s="3">
-        <v>133300</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>45000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>124000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>134000</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -930,66 +955,73 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1364000</v>
+        <v>1393000</v>
       </c>
       <c r="E17" s="3">
+        <v>1361000</v>
+      </c>
+      <c r="F17" s="3">
         <v>1294000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1260000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1277000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1274000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1242000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1327000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>804000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>720000</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>965000</v>
+        <v>860000</v>
       </c>
       <c r="E18" s="3">
+        <v>968000</v>
+      </c>
+      <c r="F18" s="3">
         <v>1071000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1122000</v>
       </c>
-      <c r="G18" s="3">
-        <v>1011000</v>
-      </c>
       <c r="H18" s="3">
+        <v>1014000</v>
+      </c>
+      <c r="I18" s="3">
         <v>1159000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1086000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-302000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>432000</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1001,66 +1033,73 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E20" s="3">
         <v>46000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>48000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>58000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>99000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>53000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>40000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>23000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>961000</v>
+        <v>853000</v>
       </c>
       <c r="E21" s="3">
+        <v>964000</v>
+      </c>
+      <c r="F21" s="3">
         <v>1029000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1064000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1045300</v>
-      </c>
       <c r="H21" s="3">
+        <v>1033300</v>
+      </c>
+      <c r="I21" s="3">
         <v>1239300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1091000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-201000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>555000</v>
       </c>
     </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1088,66 +1127,75 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>736000</v>
+      </c>
+      <c r="E23" s="3">
         <v>873000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>979000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1004000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>713000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>997000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>896000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9471000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>392000</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E24" s="3">
         <v>234000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>272000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>273000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>199000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>245000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>214000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-47000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>135000</v>
       </c>
     </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1175,66 +1223,75 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>700000</v>
+      </c>
+      <c r="E26" s="3">
         <v>639000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>707000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>731000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>514000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>752000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>682000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9518000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>685000</v>
+      </c>
+      <c r="E27" s="3">
         <v>624000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>691000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>716000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>499000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>737000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>667000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>9504000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>243000</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1262,8 +1319,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1291,8 +1351,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1320,8 +1383,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1349,66 +1415,75 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-46000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-48000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-58000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-99000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-53000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-40000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-23000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-11000</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>700000</v>
+      </c>
+      <c r="E33" s="3">
         <v>639000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>707000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>731000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>514000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>752000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>682000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9518000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1436,71 +1511,80 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>700000</v>
+      </c>
+      <c r="E35" s="3">
         <v>639000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>707000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>731000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>514000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>752000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>682000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9518000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1512,8 +1596,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1525,269 +1610,297 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>814000</v>
+      </c>
+      <c r="E41" s="3">
         <v>862000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>764000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>698000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>908000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>791000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>917000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1598000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>518000</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>22182000</v>
+      </c>
+      <c r="E42" s="3">
         <v>26648000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>26399000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>31845000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>34722000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>38157000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>38902000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>39069000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5184000</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>574000</v>
+      </c>
+      <c r="E43" s="3">
         <v>475000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>467000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>182000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>323000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>592000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>321000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>455000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>373000</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E44" s="3">
         <v>62000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>64000</v>
-      </c>
-      <c r="F44" s="3">
-        <v>58000</v>
       </c>
       <c r="G44" s="3">
         <v>58000</v>
       </c>
       <c r="H44" s="3">
+        <v>58000</v>
+      </c>
+      <c r="I44" s="3">
         <v>60000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>62000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>46000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>902000</v>
+      </c>
+      <c r="E45" s="3">
         <v>904000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>925000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>914000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>832000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>833000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>732000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>772000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>936000</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>24613000</v>
+      </c>
+      <c r="E46" s="3">
         <v>29019000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>28711000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>33783000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>36919000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>40491000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>41051000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>42034000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7118000</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>46753000</v>
+      </c>
+      <c r="E47" s="3">
         <v>41026000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>40040000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>37270000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>32174000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>28905000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>24358000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>21851000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>20386000</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11645000</v>
+      </c>
+      <c r="E48" s="3">
         <v>11491000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11227000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11072000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10977000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10832000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10673000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10411000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9957000</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>622000</v>
+      </c>
+      <c r="E49" s="3">
         <v>638000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>652000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>666000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>683000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>700000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>718000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>735000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>511000</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1815,8 +1928,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1844,37 +1960,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1542000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1376000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1556000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1412000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1450000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1308000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1324000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2944000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1467000</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1902,37 +2024,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>223720000</v>
+      </c>
+      <c r="E54" s="3">
         <v>220567000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>219827000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>217836000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>213758000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>213765000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>209502000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>214658000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>109298000</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1944,8 +2072,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1957,66 +2086,73 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>155229000</v>
+      </c>
+      <c r="E57" s="3">
         <v>151574000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>151079000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>149609000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>145854000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>146233000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>141164000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>140050000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>89408000</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2079000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2148000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2197000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2238000</v>
       </c>
-      <c r="G58" s="3">
-        <v>2277000</v>
-      </c>
       <c r="H58" s="3">
+        <v>2210000</v>
+      </c>
+      <c r="I58" s="3">
         <v>2647000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2346000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3402000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3667000</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2044,95 +2180,107 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>157442000</v>
+      </c>
+      <c r="E60" s="3">
         <v>154136000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>153795000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>152537000</v>
       </c>
-      <c r="G60" s="3">
-        <v>148665000</v>
-      </c>
       <c r="H60" s="3">
+        <v>148201000</v>
+      </c>
+      <c r="I60" s="3">
         <v>149488000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>144022000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>144078000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>93407000</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>36970000</v>
+      </c>
+      <c r="E61" s="3">
         <v>37143000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>37457000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>37505000</v>
       </c>
-      <c r="G61" s="3">
-        <v>37498000</v>
-      </c>
       <c r="H61" s="3">
+        <v>37565000</v>
+      </c>
+      <c r="I61" s="3">
         <v>37670000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>40053000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>44954000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4811000</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3546000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2899000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2744000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2401000</v>
       </c>
-      <c r="G62" s="3">
-        <v>2761000</v>
-      </c>
       <c r="H62" s="3">
+        <v>3158000</v>
+      </c>
+      <c r="I62" s="3">
         <v>2591000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2509000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2859000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1132000</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2160,8 +2308,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2189,8 +2340,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2218,37 +2372,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>201492000</v>
+      </c>
+      <c r="E66" s="3">
         <v>197739000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>197340000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>195988000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>192503000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>193376000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>189731000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>195442000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>99636000</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2260,8 +2420,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2289,8 +2450,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2318,8 +2482,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2347,8 +2514,11 @@
       <c r="K70" s="3">
         <v>881000</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>881000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2376,37 +2546,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19361000</v>
+      </c>
+      <c r="E72" s="3">
         <v>18703000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18102000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>17435000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>16742000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>16267000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15541000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>14885000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5392000</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2434,8 +2610,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2463,8 +2642,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2492,37 +2674,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21347000</v>
+      </c>
+      <c r="E76" s="3">
         <v>21947000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21606000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>20967000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20374000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>19508000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18890000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18335000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8781000</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2550,71 +2738,80 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>700000</v>
+      </c>
+      <c r="E81" s="3">
         <v>639000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>707000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>731000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>514000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>752000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>682000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9518000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2626,37 +2823,41 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-214000</v>
+      </c>
+      <c r="E83" s="3">
         <v>-102000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-34000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>119000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>129000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>131000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>143000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>108000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2684,8 +2885,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2713,8 +2917,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2742,8 +2949,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2771,8 +2981,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2800,37 +3013,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1119000</v>
+      </c>
+      <c r="E89" s="3">
         <v>991000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>417000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>461000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>901000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1205000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>916000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-362000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1054000</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2842,37 +3061,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-441000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-471000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-338000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-285000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-416000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-298000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-382000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-332000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-381000</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2900,8 +3123,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2929,37 +3155,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3744000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-301000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1819000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4291000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-358000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3754000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3913000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2628000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-730000</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2971,37 +3203,41 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>23000</v>
+        <v>27000</v>
       </c>
       <c r="E96" s="3">
         <v>23000</v>
       </c>
       <c r="F96" s="3">
-        <v>24000</v>
+        <v>23000</v>
       </c>
       <c r="G96" s="3">
         <v>24000</v>
       </c>
       <c r="H96" s="3">
-        <v>11000</v>
+        <v>24000</v>
       </c>
       <c r="I96" s="3">
         <v>11000</v>
       </c>
       <c r="J96" s="3">
+        <v>11000</v>
+      </c>
+      <c r="K96" s="3">
         <v>12000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3029,8 +3265,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3058,8 +3297,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3087,37 +3329,43 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2577000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-592000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1468000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3620000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-426000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2424000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5511000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1186000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-287000</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3145,33 +3393,39 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="E102" s="3">
         <v>98000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>66000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-210000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>117000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-125000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-682000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1080000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>37000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FCNC.A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FCNC.A_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
   <si>
     <t>FCNC.A</t>
   </si>
@@ -656,91 +656,97 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2144000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2253000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2329000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2365000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2382000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2288000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2401000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2413000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>502000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1152000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -771,40 +777,46 @@
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2144000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2253000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2329000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2365000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2382000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2288000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2401000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2413000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>502000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1152000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -817,8 +829,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -849,8 +862,11 @@
       <c r="L12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -881,72 +897,81 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E14" s="3">
         <v>75000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>49000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>44000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>60000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>202000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>109000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>150000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-9796000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>42000</v>
+        <v>93000</v>
       </c>
       <c r="E15" s="3">
         <v>42000</v>
       </c>
       <c r="F15" s="3">
+        <v>42000</v>
+      </c>
+      <c r="G15" s="3">
         <v>6000</v>
       </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
       <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
         <v>118300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>133300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>45000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>124000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>134000</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -956,72 +981,79 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1398000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1393000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1361000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1294000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1260000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1274000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1242000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1327000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>804000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>720000</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>746000</v>
+      </c>
+      <c r="E18" s="3">
         <v>860000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>968000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1071000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1122000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1014000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1159000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1086000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-302000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>432000</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1034,72 +1066,79 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E20" s="3">
         <v>49000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>46000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>48000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>58000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>99000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>53000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>40000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>23000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>786000</v>
+      </c>
+      <c r="E21" s="3">
         <v>853000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>964000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1029000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1064000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1033300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1239300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1091000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-201000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>555000</v>
       </c>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1130,72 +1169,81 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>651000</v>
+      </c>
+      <c r="E23" s="3">
         <v>736000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>873000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>979000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1004000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>713000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>997000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>896000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9471000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>392000</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E24" s="3">
         <v>36000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>234000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>272000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>273000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>199000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>245000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>214000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-47000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>135000</v>
       </c>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1226,72 +1274,81 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>483000</v>
+      </c>
+      <c r="E26" s="3">
         <v>700000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>639000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>707000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>731000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>514000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>752000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>682000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9518000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>468000</v>
+      </c>
+      <c r="E27" s="3">
         <v>685000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>624000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>691000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>716000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>499000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>737000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>667000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>9504000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>243000</v>
       </c>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1322,8 +1379,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1354,8 +1414,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1386,8 +1449,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1418,72 +1484,81 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-53000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-49000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-46000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-48000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-58000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-99000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-53000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-40000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-23000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-11000</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>483000</v>
+      </c>
+      <c r="E33" s="3">
         <v>700000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>639000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>707000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>731000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>514000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>752000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>682000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>9518000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1514,77 +1589,86 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>483000</v>
+      </c>
+      <c r="E35" s="3">
         <v>700000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>639000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>707000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>731000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>514000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>752000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>682000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>9518000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1597,8 +1681,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1611,296 +1696,324 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>812000</v>
+      </c>
+      <c r="E41" s="3">
         <v>814000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>862000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>764000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>698000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>908000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>791000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>917000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1598000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>518000</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>25590000</v>
+      </c>
+      <c r="E42" s="3">
         <v>22182000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>26648000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>26399000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>31845000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>34722000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>38157000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>38902000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>39069000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>5184000</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>587000</v>
+      </c>
+      <c r="E43" s="3">
         <v>574000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>475000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>467000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>182000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>323000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>592000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>321000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>455000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>373000</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>56000</v>
+        <v>202000</v>
       </c>
       <c r="E44" s="3">
+        <v>64000</v>
+      </c>
+      <c r="F44" s="3">
         <v>62000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>64000</v>
-      </c>
-      <c r="G44" s="3">
-        <v>58000</v>
       </c>
       <c r="H44" s="3">
         <v>58000</v>
       </c>
       <c r="I44" s="3">
+        <v>62000</v>
+      </c>
+      <c r="J44" s="3">
         <v>60000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>62000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>46000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>920000</v>
+      </c>
+      <c r="E45" s="3">
         <v>902000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>904000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>925000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>914000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>832000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>833000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>732000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>772000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>936000</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>24613000</v>
+        <v>28296000</v>
       </c>
       <c r="E46" s="3">
+        <v>24621000</v>
+      </c>
+      <c r="F46" s="3">
         <v>29019000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>28711000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>33783000</v>
       </c>
-      <c r="H46" s="3">
-        <v>36919000</v>
-      </c>
       <c r="I46" s="3">
+        <v>36923000</v>
+      </c>
+      <c r="J46" s="3">
         <v>40491000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>41051000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>42034000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7118000</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>47053000</v>
+      </c>
+      <c r="E47" s="3">
         <v>46753000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>41026000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>40040000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>37270000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>32174000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>28905000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>24358000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>21851000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>20386000</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11715000</v>
+      </c>
+      <c r="E48" s="3">
         <v>11645000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11491000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11227000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11072000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10977000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10832000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10673000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10411000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9957000</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>608000</v>
+      </c>
+      <c r="E49" s="3">
         <v>622000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>638000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>652000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>666000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>683000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>700000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>718000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>735000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>511000</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1931,8 +2044,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1963,40 +2079,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1542000</v>
+        <v>1472000</v>
       </c>
       <c r="E52" s="3">
+        <v>1534000</v>
+      </c>
+      <c r="F52" s="3">
         <v>1376000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1556000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1412000</v>
       </c>
-      <c r="H52" s="3">
-        <v>1450000</v>
-      </c>
       <c r="I52" s="3">
+        <v>1446000</v>
+      </c>
+      <c r="J52" s="3">
         <v>1308000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1324000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2944000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1467000</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2027,40 +2149,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>228822000</v>
+      </c>
+      <c r="E54" s="3">
         <v>223720000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>220567000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>219827000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>217836000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>213758000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>213765000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>209502000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>214658000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>109298000</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2073,8 +2201,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2087,72 +2216,79 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>159325000</v>
+      </c>
+      <c r="E57" s="3">
         <v>155229000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>151574000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>151079000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>149609000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>145854000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>146233000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>141164000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>140050000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>89408000</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2136000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2079000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2148000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2197000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2238000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2210000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2647000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2346000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3402000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3667000</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2183,104 +2319,116 @@
       <c r="L59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>161568000</v>
+      </c>
+      <c r="E60" s="3">
         <v>157442000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>154136000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>153795000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>152537000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>148201000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>149488000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>144022000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>144078000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>93407000</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>38296000</v>
+      </c>
+      <c r="E61" s="3">
         <v>36970000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>37143000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>37457000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>37505000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>37565000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>37670000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>40053000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>44954000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4811000</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3138000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3546000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2899000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2744000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2401000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3158000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2591000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2509000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2859000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1132000</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2311,8 +2459,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2343,8 +2494,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2375,40 +2529,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>206527000</v>
+      </c>
+      <c r="E66" s="3">
         <v>201492000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>197739000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>197340000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>195988000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>192503000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>193376000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>189731000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>195442000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>99636000</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2421,8 +2581,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2453,8 +2614,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2485,8 +2649,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2517,8 +2684,11 @@
       <c r="L70" s="3">
         <v>881000</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>881000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2549,40 +2719,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19802000</v>
+      </c>
+      <c r="E72" s="3">
         <v>19361000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18703000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18102000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>17435000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>16742000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>16267000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15541000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>14885000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5392000</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2613,8 +2789,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2645,8 +2824,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2677,40 +2859,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21414000</v>
+      </c>
+      <c r="E76" s="3">
         <v>21347000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21947000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>21606000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20967000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20374000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19508000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18890000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18335000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8781000</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2741,77 +2929,86 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>483000</v>
+      </c>
+      <c r="E81" s="3">
         <v>700000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>639000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>707000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>731000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>514000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>752000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>682000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>9518000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2824,40 +3021,44 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="E83" s="3">
         <v>-214000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-102000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-34000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>119000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>129000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>131000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>143000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>108000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2888,8 +3089,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2920,8 +3124,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2952,8 +3159,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2984,8 +3194,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3016,40 +3229,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1119000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>991000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>417000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>461000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>901000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1205000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>916000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-362000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1054000</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3062,40 +3281,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-273000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-441000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-471000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-338000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-285000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-416000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-298000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-382000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-332000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-381000</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3126,8 +3349,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3158,40 +3384,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4877000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3744000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-301000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1819000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4291000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-358000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3754000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>3913000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2628000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-730000</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3204,8 +3436,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3213,31 +3446,34 @@
         <v>27000</v>
       </c>
       <c r="E96" s="3">
-        <v>23000</v>
+        <v>27000</v>
       </c>
       <c r="F96" s="3">
         <v>23000</v>
       </c>
       <c r="G96" s="3">
-        <v>24000</v>
+        <v>23000</v>
       </c>
       <c r="H96" s="3">
         <v>24000</v>
       </c>
       <c r="I96" s="3">
-        <v>11000</v>
+        <v>24000</v>
       </c>
       <c r="J96" s="3">
         <v>11000</v>
       </c>
       <c r="K96" s="3">
+        <v>11000</v>
+      </c>
+      <c r="L96" s="3">
         <v>12000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3268,8 +3504,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3300,8 +3539,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3332,40 +3574,46 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4777000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2577000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-592000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1468000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3620000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-426000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2424000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5511000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1186000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-287000</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3396,36 +3644,42 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-48000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>98000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>66000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-210000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>117000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-125000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-682000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1080000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>37000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FCNC.A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FCNC.A_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>FCNC.A</t>
   </si>
@@ -656,97 +656,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2258000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2144000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2253000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2329000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2365000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2382000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2288000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2401000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2413000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>502000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1152000</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -780,43 +786,49 @@
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2258000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2144000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2253000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2329000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2365000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2382000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2288000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2401000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2413000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>502000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1152000</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -830,8 +842,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -865,8 +878,11 @@
       <c r="M12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -900,78 +916,87 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E14" s="3">
         <v>42000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>75000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>49000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>44000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>60000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>202000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>109000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>150000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-9796000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E15" s="3">
         <v>93000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>42000</v>
       </c>
       <c r="F15" s="3">
         <v>42000</v>
       </c>
       <c r="G15" s="3">
+        <v>42000</v>
+      </c>
+      <c r="H15" s="3">
         <v>6000</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
       <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
         <v>118300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>133300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>45000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>124000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>134000</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -982,78 +1007,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1411000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1398000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1393000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1361000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1294000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1260000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1274000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1242000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1327000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>804000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>720000</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>847000</v>
+      </c>
+      <c r="E18" s="3">
         <v>746000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>860000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>968000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1071000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1122000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1014000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1159000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1086000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-302000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>432000</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1067,78 +1099,85 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E20" s="3">
         <v>53000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>49000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>46000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>48000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>58000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>99000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>53000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>40000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>23000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>896000</v>
+      </c>
+      <c r="E21" s="3">
         <v>786000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>853000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>964000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1029000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1064000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1033300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1239300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1091000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-201000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>555000</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1172,78 +1211,87 @@
       <c r="M22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>758000</v>
+      </c>
+      <c r="E23" s="3">
         <v>651000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>736000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>873000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>979000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1004000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>713000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>997000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>896000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9471000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>392000</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>183000</v>
+      </c>
+      <c r="E24" s="3">
         <v>168000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>36000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>234000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>272000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>273000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>199000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>245000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>214000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-47000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>135000</v>
       </c>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1277,78 +1325,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>575000</v>
+      </c>
+      <c r="E26" s="3">
         <v>483000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>700000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>639000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>707000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>731000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>514000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>752000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>682000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9518000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>561000</v>
+      </c>
+      <c r="E27" s="3">
         <v>468000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>685000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>624000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>691000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>716000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>499000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>737000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>667000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9504000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>243000</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1382,8 +1439,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1417,8 +1477,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1452,8 +1515,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1487,78 +1553,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-53000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-49000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-46000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-48000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-58000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-99000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-53000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-40000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-23000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-11000</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>575000</v>
+      </c>
+      <c r="E33" s="3">
         <v>483000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>700000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>639000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>707000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>731000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>514000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>752000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>682000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9518000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1592,83 +1667,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>575000</v>
+      </c>
+      <c r="E35" s="3">
         <v>483000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>700000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>639000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>707000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>731000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>514000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>752000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>682000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9518000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1682,8 +1766,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1697,323 +1782,351 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>889000</v>
+      </c>
+      <c r="E41" s="3">
         <v>812000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>814000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>862000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>764000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>698000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>908000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>791000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>917000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1598000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>518000</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>27110000</v>
+      </c>
+      <c r="E42" s="3">
         <v>25590000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>22182000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>26648000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>26399000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>31845000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>34722000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>38157000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>38902000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>39069000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5184000</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>664000</v>
+      </c>
+      <c r="E43" s="3">
         <v>587000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>574000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>475000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>467000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>182000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>323000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>592000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>321000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>455000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>373000</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>103000</v>
+      </c>
+      <c r="E44" s="3">
         <v>202000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>64000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>62000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>64000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>58000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>62000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>60000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>62000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>46000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>902000</v>
+      </c>
+      <c r="E45" s="3">
         <v>920000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>902000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>904000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>925000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>914000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>832000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>833000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>732000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>772000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>936000</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>29793000</v>
+      </c>
+      <c r="E46" s="3">
         <v>28296000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>24621000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>29019000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>28711000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>33783000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>36923000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>40491000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>41051000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>42034000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7118000</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>46097000</v>
+      </c>
+      <c r="E47" s="3">
         <v>47053000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>46753000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>41026000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>40040000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>37270000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>32174000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>28905000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>24358000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>21851000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>20386000</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11899000</v>
+      </c>
+      <c r="E48" s="3">
         <v>11715000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11645000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11491000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11227000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11072000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10977000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10832000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10673000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10411000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9957000</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>596000</v>
+      </c>
+      <c r="E49" s="3">
         <v>608000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>622000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>638000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>652000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>666000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>683000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>700000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>718000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>735000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>511000</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2047,8 +2160,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2082,43 +2198,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1671000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1472000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1534000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1376000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1556000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1412000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1446000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1308000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1324000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2944000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1467000</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2152,43 +2274,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>229653000</v>
+      </c>
+      <c r="E54" s="3">
         <v>228822000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>223720000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>220567000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>219827000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>217836000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>213758000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>213765000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>209502000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>214658000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>109298000</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2202,8 +2330,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2217,78 +2346,85 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>159935000</v>
+      </c>
+      <c r="E57" s="3">
         <v>159325000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>155229000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>151574000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>151079000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>149609000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>145854000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>146233000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>141164000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>140050000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>89408000</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2179000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2136000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2079000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2148000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2197000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2238000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2210000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2647000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2346000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3402000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3667000</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2322,113 +2458,125 @@
       <c r="M59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>162234000</v>
+      </c>
+      <c r="E60" s="3">
         <v>161568000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>157442000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>154136000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>153795000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>152537000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>148201000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>149488000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>144022000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>144078000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>93407000</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>37997000</v>
+      </c>
+      <c r="E61" s="3">
         <v>38296000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>36970000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>37143000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>37457000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>37505000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>37565000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>37670000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>40053000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>44954000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4811000</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3566000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3138000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3546000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2899000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2744000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2401000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3158000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2591000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2509000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2859000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1132000</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2462,8 +2610,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2497,8 +2648,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2532,43 +2686,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>207357000</v>
+      </c>
+      <c r="E66" s="3">
         <v>206527000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>201492000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>197739000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>197340000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>195988000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>192503000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>193376000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>189731000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>195442000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>99636000</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2582,8 +2742,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2617,8 +2778,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2652,8 +2816,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2687,8 +2854,11 @@
       <c r="M70" s="3">
         <v>881000</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>881000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2722,43 +2892,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>20337000</v>
+      </c>
+      <c r="E72" s="3">
         <v>19802000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>19361000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18703000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18102000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>17435000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>16742000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>16267000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>15541000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>14885000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5392000</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2792,8 +2968,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2827,8 +3006,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2862,43 +3044,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21415000</v>
+      </c>
+      <c r="E76" s="3">
         <v>21414000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21347000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>21947000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>21606000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20967000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>20374000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19508000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18890000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18335000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8781000</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2932,83 +3120,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>575000</v>
+      </c>
+      <c r="E81" s="3">
         <v>483000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>700000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>639000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>707000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>731000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>514000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>752000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>682000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9518000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3022,43 +3219,47 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E83" s="3">
         <v>-29000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-214000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-102000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-34000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>119000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>129000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>131000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>143000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>108000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3092,8 +3293,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3127,8 +3331,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3162,8 +3369,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3197,8 +3407,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3232,43 +3445,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>859000</v>
+      </c>
+      <c r="E89" s="3">
         <v>98000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1119000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>991000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>417000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>461000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>901000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1205000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>916000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-362000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1054000</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3282,43 +3501,47 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-341000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-273000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-441000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-471000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-338000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-285000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-416000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-298000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-382000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-332000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-381000</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3352,8 +3575,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3387,43 +3613,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-562000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4877000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3744000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-301000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1819000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4291000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-358000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3754000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3913000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2628000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-730000</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3437,43 +3669,47 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="E96" s="3">
         <v>27000</v>
       </c>
       <c r="F96" s="3">
-        <v>23000</v>
+        <v>27000</v>
       </c>
       <c r="G96" s="3">
         <v>23000</v>
       </c>
       <c r="H96" s="3">
-        <v>24000</v>
+        <v>23000</v>
       </c>
       <c r="I96" s="3">
         <v>24000</v>
       </c>
       <c r="J96" s="3">
-        <v>11000</v>
+        <v>24000</v>
       </c>
       <c r="K96" s="3">
         <v>11000</v>
       </c>
       <c r="L96" s="3">
+        <v>11000</v>
+      </c>
+      <c r="M96" s="3">
         <v>12000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3507,8 +3743,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3542,8 +3781,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3577,43 +3819,49 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-220000</v>
+      </c>
+      <c r="E100" s="3">
         <v>4777000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2577000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-592000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1468000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3620000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-426000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2424000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5511000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1186000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-287000</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3647,39 +3895,45 @@
       <c r="M101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-48000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>98000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>66000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-210000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>117000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-125000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-682000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1080000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>37000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FCNC.A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FCNC.A_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>FCNC.A</t>
   </si>
@@ -656,109 +656,115 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2392000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2242000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2258000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2144000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2253000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2329000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2365000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2382000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2288000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2401000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2413000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>502000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1152000</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -798,49 +804,55 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2392000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2242000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2258000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2144000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2253000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2329000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2365000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2382000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2288000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2401000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2413000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>502000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1152000</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -856,8 +868,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -897,8 +910,11 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -938,90 +954,99 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E14" s="3">
         <v>28000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>38000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>42000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>75000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>46000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>44000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>60000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>202000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>109000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>150000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-9796000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E15" s="3">
         <v>91000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>100000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>93000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>42000</v>
       </c>
       <c r="H15" s="3">
         <v>42000</v>
       </c>
       <c r="I15" s="3">
+        <v>42000</v>
+      </c>
+      <c r="J15" s="3">
         <v>6000</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
         <v>118300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>133300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>45000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>124000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>134000</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1034,90 +1059,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1493000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1412000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1411000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1398000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1393000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1364000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1294000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1260000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1274000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1242000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1327000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>804000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>720000</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>899000</v>
+      </c>
+      <c r="E18" s="3">
         <v>830000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>847000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>746000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>860000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>965000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1071000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1122000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1014000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1159000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1086000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-302000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>432000</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1133,90 +1165,97 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>51000</v>
+        <v>40000</v>
       </c>
       <c r="E20" s="3">
         <v>51000</v>
       </c>
       <c r="F20" s="3">
+        <v>51000</v>
+      </c>
+      <c r="G20" s="3">
         <v>53000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>49000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>46000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>48000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>58000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>99000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>53000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>40000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>23000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>894300</v>
+      </c>
+      <c r="E21" s="3">
         <v>870000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>896000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>786000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>853000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>961000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1029000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1064000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1033300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1239300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1091000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-201000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>555000</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1256,90 +1295,99 @@
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>811000</v>
+      </c>
+      <c r="E23" s="3">
         <v>751000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>758000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>651000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>736000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>873000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>979000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1004000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>713000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>997000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>896000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>9471000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>392000</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>183000</v>
+        <v>231000</v>
       </c>
       <c r="E24" s="3">
         <v>183000</v>
       </c>
       <c r="F24" s="3">
+        <v>183000</v>
+      </c>
+      <c r="G24" s="3">
         <v>168000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>36000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>234000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>272000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>273000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>199000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>245000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>214000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-47000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>135000</v>
       </c>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1379,90 +1427,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>580000</v>
+      </c>
+      <c r="E26" s="3">
         <v>568000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>575000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>483000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>700000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>639000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>707000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>731000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>514000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>752000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>682000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>9518000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>566000</v>
+      </c>
+      <c r="E27" s="3">
         <v>554000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>561000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>468000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>685000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>624000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>691000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>716000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>499000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>737000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>667000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>9504000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>243000</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1502,8 +1559,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1543,8 +1603,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1584,8 +1647,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1625,90 +1691,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-51000</v>
+        <v>-40000</v>
       </c>
       <c r="E32" s="3">
         <v>-51000</v>
       </c>
       <c r="F32" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-53000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-49000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-46000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-48000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-58000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-99000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-53000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-40000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-23000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-11000</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>580000</v>
+      </c>
+      <c r="E33" s="3">
         <v>568000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>575000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>483000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>700000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>639000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>707000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>731000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>514000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>752000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>682000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>9518000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1748,95 +1823,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>580000</v>
+      </c>
+      <c r="E35" s="3">
         <v>568000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>575000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>483000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>700000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>639000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>707000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>731000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>514000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>752000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>682000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>9518000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1852,8 +1936,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1869,377 +1954,405 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>801000</v>
+      </c>
+      <c r="E41" s="3">
         <v>874000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>889000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>812000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>814000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>862000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>764000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>698000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>908000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>791000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>917000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1598000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>518000</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>20567000</v>
+      </c>
+      <c r="E42" s="3">
         <v>25451000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>27110000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>25590000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>22182000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>26648000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>26399000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>31845000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>34722000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>38157000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>38902000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>39069000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>5184000</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>634000</v>
+      </c>
+      <c r="E43" s="3">
         <v>636000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>664000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>587000</v>
       </c>
-      <c r="G43" s="3">
-        <v>574000</v>
-      </c>
       <c r="H43" s="3">
+        <v>580000</v>
+      </c>
+      <c r="I43" s="3">
         <v>475000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>467000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>182000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>323000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>592000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>321000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>455000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>373000</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E44" s="3">
         <v>98000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>103000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>202000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>64000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>62000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>64000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>58000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>62000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>60000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>62000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>46000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>912000</v>
+      </c>
+      <c r="E45" s="3">
         <v>945000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>902000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>920000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>902000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>904000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>925000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>914000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>832000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>833000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>732000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>772000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>936000</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>23842000</v>
+      </c>
+      <c r="E46" s="3">
         <v>28116000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>29793000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>28296000</v>
       </c>
-      <c r="G46" s="3">
-        <v>24621000</v>
-      </c>
       <c r="H46" s="3">
+        <v>24627000</v>
+      </c>
+      <c r="I46" s="3">
         <v>29019000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>28711000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>33783000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>36923000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>40491000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>41051000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>42034000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7118000</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>44706000</v>
+      </c>
+      <c r="E47" s="3">
         <v>48135000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>46097000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>47053000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>46753000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>41026000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>40040000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>37270000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>32174000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>28905000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>24358000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>21851000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>20386000</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12362000</v>
+      </c>
+      <c r="E48" s="3">
         <v>12034000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11899000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11715000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11645000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11491000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>11227000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>11072000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10977000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10832000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10673000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10411000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9957000</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>573000</v>
+      </c>
+      <c r="E49" s="3">
         <v>584000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>596000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>608000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>622000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>638000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>652000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>666000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>683000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>700000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>718000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>735000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>511000</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2279,8 +2392,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2320,49 +2436,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1851000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1513000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1671000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1472000</v>
       </c>
-      <c r="G52" s="3">
-        <v>1534000</v>
-      </c>
       <c r="H52" s="3">
+        <v>1528000</v>
+      </c>
+      <c r="I52" s="3">
         <v>1376000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1556000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1412000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1446000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1308000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1324000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2944000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1467000</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2402,49 +2524,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>229698000</v>
+      </c>
+      <c r="E54" s="3">
         <v>233488000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>229653000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>228822000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>223720000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>220567000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>219827000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>217836000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>213758000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>213765000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>209502000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>214658000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>109298000</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2460,8 +2588,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2477,90 +2606,97 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>161578000</v>
+      </c>
+      <c r="E57" s="3">
         <v>163190000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>159935000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>159325000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>155229000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>151574000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>151079000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>149609000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>145854000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>146233000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>141164000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>140050000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>89408000</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1947000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2269000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2179000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2136000</v>
       </c>
-      <c r="G58" s="3">
-        <v>2079000</v>
-      </c>
       <c r="H58" s="3">
+        <v>2008000</v>
+      </c>
+      <c r="I58" s="3">
         <v>2148000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2197000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2238000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2210000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2647000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2346000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3402000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3667000</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2600,131 +2736,143 @@
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>163665000</v>
+      </c>
+      <c r="E60" s="3">
         <v>165564000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>162234000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>161568000</v>
       </c>
-      <c r="G60" s="3">
-        <v>157442000</v>
-      </c>
       <c r="H60" s="3">
+        <v>157371000</v>
+      </c>
+      <c r="I60" s="3">
         <v>154136000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>153795000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>152537000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>148201000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>149488000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>144022000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>144078000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>93407000</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>36032000</v>
+      </c>
+      <c r="E61" s="3">
         <v>38593000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>37997000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>38296000</v>
       </c>
-      <c r="G61" s="3">
-        <v>36970000</v>
-      </c>
       <c r="H61" s="3">
+        <v>37041000</v>
+      </c>
+      <c r="I61" s="3">
         <v>37143000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>37457000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>37505000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>37565000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>37670000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>40053000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>44954000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4811000</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7763000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3765000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3566000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3138000</v>
       </c>
-      <c r="G62" s="3">
-        <v>3546000</v>
-      </c>
       <c r="H62" s="3">
+        <v>7080000</v>
+      </c>
+      <c r="I62" s="3">
         <v>2899000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2744000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2401000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3158000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2591000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2509000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2859000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1132000</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2764,8 +2912,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2805,8 +2956,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2846,49 +3000,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>207460000</v>
+      </c>
+      <c r="E66" s="3">
         <v>211502000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>207357000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>206527000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>201492000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>197739000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>197340000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>195988000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>192503000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>193376000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>189731000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>195442000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>99636000</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2904,8 +3064,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2945,8 +3106,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2986,13 +3150,16 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>881000</v>
+        <v>1375000</v>
       </c>
       <c r="E70" s="3">
         <v>881000</v>
@@ -3027,8 +3194,11 @@
       <c r="O70" s="3">
         <v>881000</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>881000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3068,49 +3238,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>20768000</v>
+      </c>
+      <c r="E72" s="3">
         <v>20866000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>20337000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>19802000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>19361000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18703000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18102000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>17435000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16742000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16267000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>15541000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>14885000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5392000</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3150,8 +3326,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3191,8 +3370,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3232,49 +3414,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20863000</v>
+      </c>
+      <c r="E76" s="3">
         <v>21105000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21415000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>21414000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>21347000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>21947000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>21606000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>20967000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20374000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19508000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18890000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18335000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8781000</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3314,95 +3502,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>580000</v>
+      </c>
+      <c r="E81" s="3">
         <v>568000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>575000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>483000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>700000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>639000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>707000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>731000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>514000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>752000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>682000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>9518000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3418,49 +3615,53 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-143000</v>
+      </c>
+      <c r="E83" s="3">
         <v>27000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-29000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-214000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-102000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-34000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>119000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>129000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>131000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>143000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>108000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3500,8 +3701,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3541,8 +3745,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3582,8 +3789,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3623,8 +3833,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3664,49 +3877,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1050000</v>
+      </c>
+      <c r="E89" s="3">
         <v>916000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>859000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>98000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1119000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>991000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>417000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>461000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>901000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1205000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>916000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-362000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1054000</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3722,49 +3941,53 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-573000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-375000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-341000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-273000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-441000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-471000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-338000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-285000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-416000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-298000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-382000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-332000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-381000</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3804,8 +4027,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3845,49 +4071,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>3629000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3801000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-562000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4877000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3744000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-301000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1819000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4291000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-358000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3754000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>3913000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>2628000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-730000</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3903,49 +4135,53 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E96" s="3">
         <v>25000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>26000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>27000</v>
       </c>
       <c r="G96" s="3">
         <v>27000</v>
       </c>
       <c r="H96" s="3">
-        <v>23000</v>
+        <v>27000</v>
       </c>
       <c r="I96" s="3">
         <v>23000</v>
       </c>
       <c r="J96" s="3">
-        <v>24000</v>
+        <v>23000</v>
       </c>
       <c r="K96" s="3">
         <v>24000</v>
       </c>
       <c r="L96" s="3">
-        <v>11000</v>
+        <v>24000</v>
       </c>
       <c r="M96" s="3">
         <v>11000</v>
       </c>
       <c r="N96" s="3">
+        <v>11000</v>
+      </c>
+      <c r="O96" s="3">
         <v>12000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3985,8 +4221,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4026,8 +4265,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4067,49 +4309,55 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4752000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2870000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-220000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4777000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2577000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-592000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1468000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3620000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-426000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2424000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5511000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1186000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-287000</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4149,45 +4397,51 @@
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-73000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-15000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>77000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-48000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>98000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>66000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-210000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>117000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-125000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-682000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1080000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>37000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FCNC.A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FCNC.A_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>FCNC.A</t>
   </si>
@@ -656,115 +656,121 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2249000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2392000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2242000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2258000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2144000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2253000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2329000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2365000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2382000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2288000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2401000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2413000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>502000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1152000</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -807,52 +813,58 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2249000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2392000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2242000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2258000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2144000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2253000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2329000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2365000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2382000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2288000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2401000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2413000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>502000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1152000</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -869,8 +881,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -913,8 +926,11 @@
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -957,96 +973,105 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E14" s="3">
         <v>48000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>28000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>38000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>42000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>75000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>46000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>44000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>60000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>202000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>109000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>150000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-9796000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E15" s="3">
         <v>35300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>91000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>100000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>93000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>42000</v>
       </c>
       <c r="I15" s="3">
         <v>42000</v>
       </c>
       <c r="J15" s="3">
+        <v>42000</v>
+      </c>
+      <c r="K15" s="3">
         <v>6000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
         <v>118300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>133300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>45000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>124000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>134000</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1060,96 +1085,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1480000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1493000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1412000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1411000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1398000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1393000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1364000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1294000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1260000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1274000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1242000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1327000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>804000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>720000</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>769000</v>
+      </c>
+      <c r="E18" s="3">
         <v>899000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>830000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>847000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>746000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>860000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>965000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1071000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1122000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1014000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1159000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1086000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-302000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>432000</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1166,96 +1198,103 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E20" s="3">
         <v>40000</v>
-      </c>
-      <c r="E20" s="3">
-        <v>51000</v>
       </c>
       <c r="F20" s="3">
         <v>51000</v>
       </c>
       <c r="G20" s="3">
+        <v>51000</v>
+      </c>
+      <c r="H20" s="3">
         <v>53000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>49000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>46000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>48000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>58000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>99000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>53000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>40000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>23000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>898000</v>
+      </c>
+      <c r="E21" s="3">
         <v>894300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>870000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>896000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>786000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>853000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>961000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1029000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1064000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1033300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1239300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1091000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-201000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>555000</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1298,96 +1337,105 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>705000</v>
+      </c>
+      <c r="E23" s="3">
         <v>811000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>751000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>758000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>651000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>736000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>873000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>979000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1004000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>713000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>997000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>896000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>9471000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>392000</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>171000</v>
+      </c>
+      <c r="E24" s="3">
         <v>231000</v>
-      </c>
-      <c r="E24" s="3">
-        <v>183000</v>
       </c>
       <c r="F24" s="3">
         <v>183000</v>
       </c>
       <c r="G24" s="3">
+        <v>183000</v>
+      </c>
+      <c r="H24" s="3">
         <v>168000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>36000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>234000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>272000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>273000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>199000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>245000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>214000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-47000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>135000</v>
       </c>
     </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1430,96 +1478,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>534000</v>
+      </c>
+      <c r="E26" s="3">
         <v>580000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>568000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>575000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>483000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>700000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>639000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>707000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>731000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>514000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>752000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>682000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>9518000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>508000</v>
+      </c>
+      <c r="E27" s="3">
         <v>566000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>554000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>561000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>468000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>685000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>624000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>691000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>716000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>499000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>737000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>667000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>9504000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>243000</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1562,8 +1619,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1606,8 +1666,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1650,8 +1713,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1694,96 +1760,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-40000</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-51000</v>
       </c>
       <c r="F32" s="3">
         <v>-51000</v>
       </c>
       <c r="G32" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="H32" s="3">
         <v>-53000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-49000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-46000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-48000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-58000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-99000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-53000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-40000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-23000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-11000</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>534000</v>
+      </c>
+      <c r="E33" s="3">
         <v>580000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>568000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>575000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>483000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>700000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>639000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>707000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>731000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>514000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>752000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>682000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>9518000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1826,101 +1901,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>534000</v>
+      </c>
+      <c r="E35" s="3">
         <v>580000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>568000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>575000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>483000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>700000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>639000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>707000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>731000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>514000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>752000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>682000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>9518000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1937,8 +2021,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1955,404 +2040,432 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1080000</v>
+      </c>
+      <c r="E41" s="3">
         <v>801000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>874000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>889000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>812000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>814000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>862000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>764000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>698000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>908000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>791000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>917000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1598000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>518000</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>23910000</v>
+      </c>
+      <c r="E42" s="3">
         <v>20567000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>25451000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>27110000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>25590000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>22182000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>26648000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>26399000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>31845000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>34722000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>38157000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>38902000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>39069000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>5184000</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>628000</v>
+      </c>
+      <c r="E43" s="3">
         <v>634000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>636000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>664000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>587000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>580000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>475000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>467000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>182000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>323000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>592000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>321000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>455000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>373000</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E44" s="3">
         <v>124000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>98000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>103000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>202000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>64000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>62000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>64000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>58000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>62000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>60000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>62000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>46000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>955000</v>
+      </c>
+      <c r="E45" s="3">
         <v>912000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>945000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>902000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>920000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>902000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>904000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>925000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>914000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>832000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>833000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>732000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>772000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>936000</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>27811000</v>
+      </c>
+      <c r="E46" s="3">
         <v>23842000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>28116000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>29793000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>28296000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>24627000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>29019000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>28711000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>33783000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>36923000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>40491000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>41051000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>42034000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7118000</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>46079000</v>
+      </c>
+      <c r="E47" s="3">
         <v>44706000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>48135000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>46097000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>47053000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>46753000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>41026000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>40040000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>37270000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>32174000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>28905000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>24358000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>21851000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>20386000</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12469000</v>
+      </c>
+      <c r="E48" s="3">
         <v>12362000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12034000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11899000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11715000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11645000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>11491000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>11227000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11072000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10977000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10832000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10673000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10411000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9957000</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>561000</v>
+      </c>
+      <c r="E49" s="3">
         <v>573000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>584000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>596000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>608000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>622000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>638000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>652000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>666000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>683000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>700000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>718000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>735000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>511000</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2395,8 +2508,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2439,52 +2555,58 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1905000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1851000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1513000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1671000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1472000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1528000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1376000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1556000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1412000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1446000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1308000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1324000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2944000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1467000</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2527,52 +2649,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>235959000</v>
+      </c>
+      <c r="E54" s="3">
         <v>229698000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>233488000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>229653000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>228822000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>223720000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>220567000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>219827000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>217836000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>213758000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>213765000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>209502000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>214658000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>109298000</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2589,8 +2717,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2607,96 +2736,103 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>171985000</v>
+      </c>
+      <c r="E57" s="3">
         <v>161578000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>163190000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>159935000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>159325000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>155229000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>151574000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>151079000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>149609000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>145854000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>146233000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>141164000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>140050000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>89408000</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1902000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1947000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2269000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2179000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2136000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2008000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2148000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2197000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2238000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2210000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2647000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2346000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3402000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3667000</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2739,140 +2875,152 @@
       <c r="P59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>173996000</v>
+      </c>
+      <c r="E60" s="3">
         <v>163665000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>165564000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>162234000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>161568000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>157371000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>154136000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>153795000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>152537000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>148201000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>149488000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>144022000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>144078000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>93407000</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>34109000</v>
+      </c>
+      <c r="E61" s="3">
         <v>36032000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>38593000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>37997000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>38296000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>37041000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>37143000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>37457000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>37505000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>37565000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>37670000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>40053000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>44954000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4811000</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5806000</v>
+      </c>
+      <c r="E62" s="3">
         <v>7763000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3765000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3566000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3138000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7080000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2899000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2744000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2401000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3158000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2591000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2509000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2859000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1132000</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2915,8 +3063,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2959,8 +3110,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3003,52 +3157,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>213911000</v>
+      </c>
+      <c r="E66" s="3">
         <v>207460000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>211502000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>207357000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>206527000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>201492000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>197739000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>197340000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>195988000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>192503000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>193376000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>189731000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>195442000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>99636000</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3065,8 +3225,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3109,8 +3270,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3153,16 +3317,19 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>1765000</v>
+      </c>
+      <c r="E70" s="3">
         <v>1375000</v>
-      </c>
-      <c r="E70" s="3">
-        <v>881000</v>
       </c>
       <c r="F70" s="3">
         <v>881000</v>
@@ -3197,8 +3364,11 @@
       <c r="P70" s="3">
         <v>881000</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>881000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3241,52 +3411,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>20343000</v>
+      </c>
+      <c r="E72" s="3">
         <v>20768000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>20866000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>20337000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>19802000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>19361000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18703000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18102000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17435000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16742000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16267000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>15541000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>14885000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5392000</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3329,8 +3505,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3373,8 +3552,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3417,52 +3599,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20283000</v>
+      </c>
+      <c r="E76" s="3">
         <v>20863000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21105000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>21415000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>21414000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>21347000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>21947000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>21606000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20967000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20374000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19508000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18890000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18335000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8781000</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3505,101 +3693,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>534000</v>
+      </c>
+      <c r="E81" s="3">
         <v>580000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>568000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>575000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>483000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>700000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>639000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>707000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>731000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>514000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>752000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>682000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>9518000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3616,52 +3813,56 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E83" s="3">
         <v>-143000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>27000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-29000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-214000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-102000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>-34000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>119000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>129000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>131000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>143000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>108000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3704,8 +3905,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3748,8 +3952,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3792,8 +3999,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3836,8 +4046,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3880,52 +4093,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>172000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1050000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>916000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>859000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>98000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1119000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>991000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>417000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>461000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>901000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1205000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>916000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-362000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1054000</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3942,52 +4161,56 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-335000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-573000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-375000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-341000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-273000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-441000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-471000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-338000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-285000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-416000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-298000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-382000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-332000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-381000</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4030,8 +4253,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4074,52 +4300,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6537000</v>
+      </c>
+      <c r="E94" s="3">
         <v>3629000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3801000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-562000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4877000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3744000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-301000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1819000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4291000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-358000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3754000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>3913000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>2628000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-730000</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4136,52 +4368,56 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E96" s="3">
         <v>26000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>25000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>26000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>27000</v>
       </c>
       <c r="H96" s="3">
         <v>27000</v>
       </c>
       <c r="I96" s="3">
-        <v>23000</v>
+        <v>27000</v>
       </c>
       <c r="J96" s="3">
         <v>23000</v>
       </c>
       <c r="K96" s="3">
-        <v>24000</v>
+        <v>23000</v>
       </c>
       <c r="L96" s="3">
         <v>24000</v>
       </c>
       <c r="M96" s="3">
-        <v>11000</v>
+        <v>24000</v>
       </c>
       <c r="N96" s="3">
         <v>11000</v>
       </c>
       <c r="O96" s="3">
+        <v>11000</v>
+      </c>
+      <c r="P96" s="3">
         <v>12000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4224,8 +4460,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4268,8 +4507,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4312,52 +4554,58 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6644000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4752000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2870000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-220000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4777000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2577000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-592000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1468000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3620000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-426000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2424000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5511000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1186000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-287000</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4400,48 +4648,54 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>279000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-73000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-15000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>77000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-48000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>98000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>66000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-210000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>117000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-125000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-682000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1080000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>37000</v>
       </c>
     </row>
